--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:30</t>
+          <t>2026-05-24 05:37:11</t>
         </is>
       </c>
     </row>
@@ -672,16 +672,16 @@
         <v>15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>2.6667</v>
@@ -693,13 +693,13 @@
         <v>15</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="3">
@@ -726,22 +726,22 @@
         <v>15</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7833</v>
+        <v>0.8133</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.795</v>
+        <v>0.82</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.7333</v>
+        <v>2.6</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>15</v>
@@ -750,10 +750,10 @@
         <v>8</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.4667</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="4">
@@ -770,7 +770,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -780,28 +780,28 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6617</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.67</v>
+        <v>0.6133</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>4</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -834,34 +834,34 @@
         <v>15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6367</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6483</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>14</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="6">
@@ -878,7 +878,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -888,25 +888,25 @@
         <v>15</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6833</v>
+        <v>0.6783</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.695</v>
+        <v>0.6883</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.1333</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>5</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -942,28 +942,28 @@
         <v>15</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6417</v>
+        <v>0.65</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.655</v>
+        <v>0.6633</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>14</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>5</v>
@@ -996,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>3</v>
@@ -1008,16 +1008,16 @@
         <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1028,15 +1028,15 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1046,10 +1046,10 @@
         <v>100</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.721</v>
+        <v>0.671</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.721</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>3</v>
@@ -1058,19 +1058,23 @@
         <v>3</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1082,7 +1086,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1096,34 +1100,34 @@
         <v>100</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.62</v>
+        <v>0.596</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.636</v>
+        <v>0.612</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>64</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1132,7 +1136,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1140,7 +1144,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1150,10 +1154,10 @@
         <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.707</v>
+        <v>0.658</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.707</v>
+        <v>0.676</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>4</v>
@@ -1162,19 +1166,23 @@
         <v>4</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1182,7 +1190,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1190,7 +1198,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1200,35 +1208,31 @@
         <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.596</v>
+        <v>0.68</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.611</v>
+        <v>0.68</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0.14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1240,11 +1244,11 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -1254,16 +1258,16 @@
         <v>100</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1.69</v>
@@ -1272,10 +1276,10 @@
         <v>1.69</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -1286,11 +1290,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -1304,31 +1308,35 @@
         <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.668</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.668</v>
+        <v>0.612</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>59</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1336,15 +1344,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1354,10 +1362,10 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.598</v>
+        <v>0.675</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.611</v>
+        <v>0.675</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>3</v>
@@ -1366,23 +1374,19 @@
         <v>3</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>1.67</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>0.12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1390,15 +1394,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1408,10 +1412,10 @@
         <v>100</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.609</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.626</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>3</v>
@@ -1420,23 +1424,19 @@
         <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0.13</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1462,10 +1462,10 @@
         <v>100</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.605</v>
+        <v>0.616</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.628</v>
+        <v>0.632</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>3</v>
@@ -1474,22 +1474,22 @@
         <v>3</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1516,10 +1516,10 @@
         <v>100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.662</v>
+        <v>0.6</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.662</v>
+        <v>0.614</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>3</v>
@@ -1528,19 +1528,23 @@
         <v>3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1566,10 +1570,10 @@
         <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.585</v>
+        <v>0.726</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.602</v>
+        <v>0.726</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
@@ -1578,23 +1582,19 @@
         <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>0.16</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2000,7 +2000,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
@@ -2121,10 +2121,10 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>3</v>
@@ -2133,23 +2133,23 @@
         <v>3</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2171,10 +2171,10 @@
         <v>100</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.62</v>
+        <v>0.671</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.636</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>3</v>
@@ -2183,16 +2183,16 @@
         <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>16</v>
@@ -2279,16 +2279,16 @@
         <v>15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>2.6667</v>
@@ -2300,13 +2300,13 @@
         <v>15</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="P5" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2498,20 +2498,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>-0.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>-0.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>1.67</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2585,20 +2585,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2614,24 +2614,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -2672,17 +2672,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -2705,16 +2705,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2730,20 +2730,20 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -2759,20 +2759,20 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -2995,16 +2995,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2.6667</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.1334</v>
+        <v>-0.0667</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -3020,20 +3020,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2.6667</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2.6667</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2.6667</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3107,20 +3107,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2.6667</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.6667</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.718333333333333</v>
+        <v>1.696666666666667</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
@@ -3217,10 +3217,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.663333333333333</v>
+        <v>1.725</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
@@ -3255,7 +3255,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2.6667</v>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -3819,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.62</v>
+        <v>0.671</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.636</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -3831,16 +3831,16 @@
         <v>3</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>16</v>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -3873,31 +3873,31 @@
         <v>0.596</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.611</v>
+        <v>0.612</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>2</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3921,34 +3921,34 @@
         <v>100</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.598</v>
+        <v>0.658</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.611</v>
+        <v>0.676</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>3</v>
@@ -3972,34 +3972,34 @@
         <v>100</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.626</v>
+        <v>0.612</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>1.69</v>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>1.65</v>
-      </c>
       <c r="K11" s="2" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>4</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -4023,10 +4023,10 @@
         <v>100</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.605</v>
+        <v>0.616</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.628</v>
+        <v>0.632</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3</v>
@@ -4035,22 +4035,22 @@
         <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>5</v>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -4074,10 +4074,10 @@
         <v>100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.585</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.602</v>
+        <v>0.614</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>3</v>
@@ -4086,22 +4086,22 @@
         <v>3</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>6</v>
@@ -4125,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>3</v>
@@ -4137,16 +4137,16 @@
         <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -4172,10 +4172,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.721</v>
+        <v>0.68</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.721</v>
+        <v>0.68</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -4184,13 +4184,13 @@
         <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>15</v>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -4219,25 +4219,25 @@
         <v>100</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.707</v>
+        <v>0.677</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.707</v>
+        <v>0.677</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>11</v>
@@ -4266,28 +4266,28 @@
         <v>100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.695</v>
+        <v>0.675</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.695</v>
+        <v>0.675</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4313,10 +4313,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.668</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.668</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3</v>
@@ -4331,10 +4331,10 @@
         <v>1.67</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4360,10 +4360,10 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.662</v>
+        <v>0.726</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.662</v>
+        <v>0.726</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>3</v>
@@ -4372,16 +4372,16 @@
         <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4407,16 +4407,16 @@
         <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>2.6667</v>
@@ -4428,13 +4428,13 @@
         <v>15</v>
       </c>
       <c r="L20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="N20" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1</v>
@@ -4458,22 +4458,22 @@
         <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.7833</v>
+        <v>0.8133</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.795</v>
+        <v>0.82</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.7333</v>
+        <v>2.6</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>15</v>
@@ -4482,10 +4482,10 @@
         <v>8</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4667</v>
+        <v>0.2667</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>2</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -4509,28 +4509,28 @@
         <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.6617</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.67</v>
+        <v>0.6133</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>4</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -4560,34 +4560,34 @@
         <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6367</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6483</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>14</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.0667</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -4611,25 +4611,25 @@
         <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.6833</v>
+        <v>0.6783</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.695</v>
+        <v>0.6883</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2.3333</v>
+        <v>2.1333</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>5</v>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -4662,28 +4662,28 @@
         <v>15</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.6417</v>
+        <v>0.65</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.655</v>
+        <v>0.6633</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>5</v>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -443,7 +443,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:11</t>
+          <t>2026-05-25 14:34:26</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
     </row>
   </sheetData>
@@ -662,20 +662,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>4</v>
@@ -684,22 +684,22 @@
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="3">
@@ -716,44 +716,44 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8133</v>
+        <v>0.7167</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.82</v>
+        <v>0.7267</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="4">
@@ -777,13 +777,13 @@
         <v>600</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6133</v>
+        <v>0.625</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>3</v>
@@ -792,22 +792,22 @@
         <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>13</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="P4" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="5">
@@ -824,20 +824,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6917</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6483</v>
+        <v>0.705</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>3</v>
@@ -846,10 +846,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>14</v>
@@ -858,10 +858,10 @@
         <v>4</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.0667</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="6">
@@ -878,44 +878,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.6483</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>0.6783</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="N6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -932,20 +932,20 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.65</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.6633</v>
+        <v>0.665</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>3</v>
@@ -960,16 +960,16 @@
         <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -996,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>3</v>
@@ -1008,16 +1008,16 @@
         <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1136,15 +1136,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1154,35 +1154,31 @@
         <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.658</v>
+        <v>0.742</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.676</v>
+        <v>0.742</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>1.76</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0.15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1190,15 +1186,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1208,31 +1204,35 @@
         <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.68</v>
+        <v>0.658</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1240,11 +1240,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -1258,19 +1258,19 @@
         <v>100</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.677</v>
+        <v>0.6</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.677</v>
+        <v>0.612</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>1.69</v>
@@ -1281,8 +1281,12 @@
       <c r="N13" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1294,11 +1298,11 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1308,34 +1312,34 @@
         <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.612</v>
+        <v>0.632</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -1348,7 +1352,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1362,10 +1366,10 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>3</v>
@@ -1374,16 +1378,16 @@
         <v>3</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -1398,7 +1402,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1412,10 +1416,10 @@
         <v>100</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>3</v>
@@ -1424,16 +1428,16 @@
         <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -1448,11 +1452,11 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
@@ -1462,10 +1466,10 @@
         <v>100</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.616</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.632</v>
+        <v>0.614</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>3</v>
@@ -1474,22 +1478,22 @@
         <v>3</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -1498,15 +1502,15 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1516,10 +1520,10 @@
         <v>100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.6</v>
+        <v>0.704</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.614</v>
+        <v>0.704</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>3</v>
@@ -1528,23 +1532,19 @@
         <v>3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1570,10 +1570,10 @@
         <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
@@ -1582,16 +1582,16 @@
         <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>51</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
@@ -2121,10 +2121,10 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>3</v>
@@ -2133,16 +2133,16 @@
         <v>3</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -2269,20 +2269,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>4</v>
@@ -2291,22 +2291,22 @@
         <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
   </sheetData>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2498,20 +2498,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2527,20 +2527,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2585,20 +2585,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2962,24 +2962,24 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2991,20 +2991,20 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.0667</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -3024,16 +3024,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.4667</v>
+        <v>-0.125</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.4667</v>
+        <v>-0.1875</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2.1333</v>
+        <v>2.0625</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.5334</v>
+        <v>-0.25</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3107,20 +3107,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.6667</v>
+        <v>-0.3125</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.696666666666667</v>
+        <v>1.701666666666666</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
@@ -3255,13 +3255,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2.3</v>
+        <v>2.1875</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4125,10 +4125,10 @@
         <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>3</v>
@@ -4137,16 +4137,16 @@
         <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -4172,10 +4172,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.68</v>
+        <v>0.742</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.68</v>
+        <v>0.742</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -4184,16 +4184,16 @@
         <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -4219,10 +4219,10 @@
         <v>100</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
@@ -4231,16 +4231,16 @@
         <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4266,10 +4266,10 @@
         <v>100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.675</v>
+        <v>0.674</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.675</v>
+        <v>0.674</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>3</v>
@@ -4278,16 +4278,16 @@
         <v>3</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4313,10 +4313,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.704</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3</v>
@@ -4325,16 +4325,16 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>56</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4360,10 +4360,10 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>3</v>
@@ -4372,16 +4372,16 @@
         <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>51</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4397,20 +4397,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>4</v>
@@ -4419,22 +4419,22 @@
         <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1</v>
@@ -4448,44 +4448,44 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.8133</v>
+        <v>0.7167</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.82</v>
+        <v>0.7267</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>2</v>
@@ -4506,13 +4506,13 @@
         <v>600</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.6133</v>
+        <v>0.625</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -4521,22 +4521,22 @@
         <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>13</v>
       </c>
       <c r="L22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M22" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="N22" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.3125</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>3</v>
@@ -4550,20 +4550,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6917</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.6483</v>
+        <v>0.705</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>3</v>
@@ -4572,10 +4572,10 @@
         <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>14</v>
@@ -4584,10 +4584,10 @@
         <v>4</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0667</v>
+        <v>0.1875</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
@@ -4601,44 +4601,44 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D24" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0.6483</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="K24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0.6783</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>5</v>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0.65</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.6633</v>
+        <v>0.665</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>3</v>
@@ -4680,16 +4680,16 @@
         <v>2</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>6</v>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -443,7 +443,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:26</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
     </row>
   </sheetData>
@@ -662,7 +662,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -672,34 +672,34 @@
         <v>16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>16</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -726,34 +726,34 @@
         <v>16</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7167</v>
+        <v>0.695</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7267</v>
+        <v>0.7017</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.5</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.375</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="4">
@@ -770,7 +770,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -780,10 +780,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.615</v>
+        <v>0.905</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.625</v>
+        <v>0.9233</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>3</v>
@@ -792,22 +792,22 @@
         <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -834,34 +834,34 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6917</v>
+        <v>0.6883</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -878,7 +878,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -888,28 +888,28 @@
         <v>16</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6483</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.6633</v>
+        <v>0.71</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>6</v>
@@ -942,34 +942,34 @@
         <v>16</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6983</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.665</v>
+        <v>0.7117</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="8">
@@ -978,7 +978,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -996,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.708</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>3</v>
@@ -1008,19 +1008,23 @@
         <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1032,11 +1036,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1046,34 +1050,34 @@
         <v>100</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.671</v>
+        <v>0.596</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -1086,11 +1090,11 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1100,10 +1104,10 @@
         <v>100</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.596</v>
+        <v>0.658</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.612</v>
+        <v>0.676</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>4</v>
@@ -1112,16 +1116,16 @@
         <v>4</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>64</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>15</v>
@@ -1140,7 +1144,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1154,28 +1158,28 @@
         <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1186,15 +1190,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1204,35 +1208,31 @@
         <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.658</v>
+        <v>0.681</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.676</v>
+        <v>0.681</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0.15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1294,15 +1294,15 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1312,10 +1312,10 @@
         <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.616</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.632</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>3</v>
@@ -1324,23 +1324,19 @@
         <v>3</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>57</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0.12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1352,11 +1348,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1366,28 +1362,28 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -1398,11 +1394,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1416,10 +1412,10 @@
         <v>100</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.674</v>
+        <v>0.616</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.674</v>
+        <v>0.632</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>3</v>
@@ -1428,19 +1424,23 @@
         <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1520,10 +1520,10 @@
         <v>100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1570,10 +1570,10 @@
         <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
@@ -1582,16 +1582,16 @@
         <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -2121,35 +2121,35 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -2279,34 +2279,34 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>16</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
   </sheetData>
@@ -2440,20 +2440,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2498,20 +2498,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2585,20 +2585,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.09</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2962,24 +2962,24 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2991,20 +2991,20 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -3020,20 +3020,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.125</v>
+        <v>-0.1875</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.1875</v>
+        <v>-0.25</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.3125</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.3125</v>
+        <v>-0.375</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.701666666666666</v>
+        <v>1.676666666666667</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
@@ -3255,10 +3255,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.40625</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>16</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -4125,28 +4125,28 @@
         <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -4172,10 +4172,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.742</v>
+        <v>0.681</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.742</v>
+        <v>0.681</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -4184,16 +4184,16 @@
         <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -4219,10 +4219,10 @@
         <v>100</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
@@ -4231,16 +4231,16 @@
         <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
@@ -4266,28 +4266,28 @@
         <v>100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.674</v>
+        <v>0.671</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.674</v>
+        <v>0.671</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4313,10 +4313,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3</v>
@@ -4325,16 +4325,16 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4360,10 +4360,10 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>3</v>
@@ -4372,16 +4372,16 @@
         <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -4407,34 +4407,34 @@
         <v>16</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>16</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -4458,34 +4458,34 @@
         <v>16</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.7167</v>
+        <v>0.695</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.7267</v>
+        <v>0.7017</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.375</v>
+        <v>0.1875</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>2</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -4509,10 +4509,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.615</v>
+        <v>0.905</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.625</v>
+        <v>0.9233</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -4521,22 +4521,22 @@
         <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.5</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>3</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -4560,34 +4560,34 @@
         <v>16</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6917</v>
+        <v>0.6883</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -4611,28 +4611,28 @@
         <v>16</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.6483</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.6633</v>
+        <v>0.71</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>6</v>
@@ -4662,34 +4662,34 @@
         <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.65</v>
+        <v>0.6983</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.665</v>
+        <v>0.7117</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3125</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>6</v>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -443,7 +443,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>
@@ -662,7 +662,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -672,22 +672,22 @@
         <v>16</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>16</v>
@@ -696,10 +696,10 @@
         <v>10</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -726,34 +726,34 @@
         <v>16</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.695</v>
+        <v>0.8383</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7017</v>
+        <v>0.86</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.5</v>
+        <v>2.6875</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.1875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -770,7 +770,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -780,28 +780,28 @@
         <v>16</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.905</v>
+        <v>0.7017</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9233</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>2.4375</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>8</v>
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -837,13 +837,13 @@
         <v>0.6883</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.695</v>
+        <v>0.7117</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>2.4375</v>
@@ -852,16 +852,16 @@
         <v>2.375</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="6">
@@ -878,7 +878,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -888,34 +888,34 @@
         <v>16</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7267</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7467</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.375</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>2.3125</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -942,10 +942,10 @@
         <v>16</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.72</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.7367</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>4</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -996,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.671</v>
+        <v>0.699</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>3</v>
@@ -1008,23 +1008,19 @@
         <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="P8" s="2" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1036,11 +1032,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1050,34 +1046,34 @@
         <v>100</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.596</v>
+        <v>0.671</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.612</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10">
@@ -1090,11 +1086,11 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1104,10 +1100,10 @@
         <v>100</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.658</v>
+        <v>0.596</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.676</v>
+        <v>0.612</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>4</v>
@@ -1116,16 +1112,16 @@
         <v>4</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>64</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>15</v>
@@ -1140,15 +1136,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1158,10 +1154,10 @@
         <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.752</v>
+        <v>0.658</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.752</v>
+        <v>0.676</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>4</v>
@@ -1170,19 +1166,23 @@
         <v>4</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1208,10 +1208,10 @@
         <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>3</v>
@@ -1220,16 +1220,16 @@
         <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -1240,15 +1240,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -1258,35 +1258,31 @@
         <v>100</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.612</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>0.08</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1298,11 +1294,11 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1312,10 +1308,10 @@
         <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>3</v>
@@ -1324,13 +1320,13 @@
         <v>3</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>11</v>
@@ -1344,7 +1340,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1362,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.671</v>
+        <v>0.6</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.671</v>
+        <v>0.612</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>4</v>
@@ -1374,19 +1370,23 @@
         <v>4</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
         <v>100</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.614</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>3</v>
@@ -1478,23 +1478,19 @@
         <v>3</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1502,15 +1498,15 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1520,10 +1516,10 @@
         <v>100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.674</v>
+        <v>0.6</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.674</v>
+        <v>0.614</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>3</v>
@@ -1532,19 +1528,23 @@
         <v>3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1552,15 +1552,15 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1570,31 +1570,35 @@
         <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.664</v>
+        <v>0.521</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.664</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1602,15 +1606,15 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1620,35 +1624,31 @@
         <v>100</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.498</v>
+        <v>0.656</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.541</v>
+        <v>0.656</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>1.58</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>0.36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1674,34 +1674,34 @@
         <v>100</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.556</v>
+        <v>0.535</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>1.56</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="22">
@@ -1728,10 +1728,10 @@
         <v>100</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.473</v>
+        <v>0.491</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.52</v>
+        <v>0.542</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>3</v>
@@ -1740,22 +1740,22 @@
         <v>3</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
@@ -1782,34 +1782,34 @@
         <v>100</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.469</v>
+        <v>0.521</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.53</v>
+        <v>0.573</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>43</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
@@ -1836,34 +1836,34 @@
         <v>100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.514</v>
+        <v>0.536</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
@@ -1890,10 +1890,10 @@
         <v>100</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.528</v>
+        <v>0.55</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>3</v>
@@ -1902,22 +1902,22 @@
         <v>3</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +2000,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -2121,35 +2121,35 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
         <v>100</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.498</v>
+        <v>0.521</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>3</v>
@@ -2237,22 +2237,22 @@
         <v>4</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -2279,22 +2279,22 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>16</v>
@@ -2303,10 +2303,10 @@
         <v>10</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2440,20 +2440,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2469,20 +2469,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2498,20 +2498,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2527,20 +2527,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.25</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2589,16 +2589,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -2817,20 +2817,20 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>1.56</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-2</v>
@@ -2875,20 +2875,20 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>-0.12</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -2933,20 +2933,20 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -2962,24 +2962,24 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2991,24 +2991,24 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>2.4375</v>
       </c>
-      <c r="D21" s="2" t="n">
-        <v>2.625</v>
-      </c>
       <c r="E21" s="2" t="n">
-        <v>-0.1875</v>
+        <v>0.1875</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3020,20 +3020,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>2.4375</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>2.375</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.0625</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>2.3125</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.3125</v>
+        <v>-0.125</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3114,13 +3114,13 @@
         <v>2.25</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.375</v>
+        <v>-0.1875</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.676666666666667</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
@@ -3236,10 +3236,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.475</v>
+        <v>1.506666666666667</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>100</v>
@@ -3255,10 +3255,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2.40625</v>
+        <v>2.458333333333333</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>16</v>
@@ -3513,10 +3513,10 @@
         <v>100</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.498</v>
+        <v>0.521</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>3</v>
@@ -3525,22 +3525,22 @@
         <v>4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>1</v>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -3564,34 +3564,34 @@
         <v>100</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.556</v>
+        <v>0.535</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.56</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>2</v>
@@ -3615,10 +3615,10 @@
         <v>100</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.473</v>
+        <v>0.491</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.52</v>
+        <v>0.542</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>3</v>
@@ -3627,22 +3627,22 @@
         <v>3</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>3</v>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -3666,34 +3666,34 @@
         <v>100</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.469</v>
+        <v>0.521</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.53</v>
+        <v>0.573</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>43</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>4</v>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -3717,34 +3717,34 @@
         <v>100</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.514</v>
+        <v>0.536</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>5</v>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -3768,10 +3768,10 @@
         <v>100</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.528</v>
+        <v>0.55</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>3</v>
@@ -3780,22 +3780,22 @@
         <v>3</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>6</v>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -4125,28 +4125,28 @@
         <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -4172,10 +4172,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -4184,16 +4184,16 @@
         <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -4219,10 +4219,10 @@
         <v>100</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
@@ -4231,16 +4231,16 @@
         <v>3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4266,25 +4266,25 @@
         <v>100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.671</v>
+        <v>0.704</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.671</v>
+        <v>0.704</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>11</v>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4313,10 +4313,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.674</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.674</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3</v>
@@ -4325,16 +4325,16 @@
         <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>58</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4360,28 +4360,28 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.664</v>
+        <v>0.656</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.664</v>
+        <v>0.656</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -4407,22 +4407,22 @@
         <v>16</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>16</v>
@@ -4431,10 +4431,10 @@
         <v>10</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -4458,34 +4458,34 @@
         <v>16</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.695</v>
+        <v>0.8383</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.7017</v>
+        <v>0.86</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.5</v>
+        <v>2.6875</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1875</v>
+        <v>0.625</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>2</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -4509,28 +4509,28 @@
         <v>16</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.905</v>
+        <v>0.7017</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.9233</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>2.4375</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>8</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -4563,13 +4563,13 @@
         <v>0.6883</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.695</v>
+        <v>0.7117</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>2.4375</v>
@@ -4578,16 +4578,16 @@
         <v>2.375</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -4611,34 +4611,34 @@
         <v>16</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7267</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.71</v>
+        <v>0.7467</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.375</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>2.3125</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>5</v>
@@ -4662,10 +4662,10 @@
         <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.6983</v>
+        <v>0.72</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.7367</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>4</v>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -443,7 +443,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
     </row>
   </sheetData>
@@ -662,20 +662,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>4</v>
@@ -684,22 +684,22 @@
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="3">
@@ -723,25 +723,25 @@
         <v>600</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.8383</v>
+        <v>0.9367</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.86</v>
+        <v>0.9533</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2.6875</v>
+        <v>2.6667</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>15</v>
@@ -750,10 +750,10 @@
         <v>8</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="4">
@@ -770,44 +770,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.7017</v>
+        <v>0.6983</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.625</v>
+        <v>2.5333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="5">
@@ -824,20 +824,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6883</v>
+        <v>0.6967</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>3</v>
@@ -846,22 +846,22 @@
         <v>3</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>15</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.375</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="6">
@@ -878,44 +878,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.7267</v>
+        <v>0.7133</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7467</v>
+        <v>0.7383</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7">
@@ -932,20 +932,20 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7367</v>
+        <v>0.7667</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>4</v>
@@ -954,10 +954,10 @@
         <v>4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.25</v>
+        <v>2.5333</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>14</v>
@@ -966,10 +966,10 @@
         <v>5</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -978,7 +978,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -996,10 +996,10 @@
         <v>100</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.699</v>
+        <v>0.618</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.699</v>
+        <v>0.632</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>3</v>
@@ -1008,19 +1008,23 @@
         <v>3</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>74</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1032,7 +1036,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1046,10 +1050,10 @@
         <v>100</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.671</v>
+        <v>0.613</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>3</v>
@@ -1061,19 +1065,19 @@
         <v>1.88</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="10">
@@ -1082,15 +1086,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
@@ -1100,10 +1104,10 @@
         <v>100</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.596</v>
+        <v>0.678</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.612</v>
+        <v>0.678</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>4</v>
@@ -1112,23 +1116,19 @@
         <v>4</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0.15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1136,15 +1136,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1154,35 +1154,31 @@
         <v>100</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.658</v>
+        <v>0.779</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.676</v>
+        <v>0.779</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0.15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1194,11 +1190,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1208,28 +1204,28 @@
         <v>100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1248,7 +1244,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -1258,31 +1254,35 @@
         <v>100</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1308,19 +1308,19 @@
         <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.704</v>
+        <v>0.616</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.704</v>
+        <v>0.637</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>1.7</v>
@@ -1329,10 +1329,14 @@
         <v>60</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1344,7 +1348,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1358,34 +1362,34 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.6</v>
+        <v>0.584</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>11</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="16">
@@ -1394,15 +1398,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1412,10 +1416,10 @@
         <v>100</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.616</v>
+        <v>0.676</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.632</v>
+        <v>0.676</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>3</v>
@@ -1424,7 +1428,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>1.66</v>
@@ -1435,12 +1439,8 @@
       <c r="N16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1448,11 +1448,11 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1466,31 +1466,35 @@
         <v>100</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1498,15 +1502,15 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1516,35 +1520,31 @@
         <v>100</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.6</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.614</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="P18" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1552,15 +1552,15 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1570,35 +1570,31 @@
         <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.521</v>
+        <v>0.694</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>0.35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1606,15 +1602,15 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1624,31 +1620,35 @@
         <v>100</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.656</v>
+        <v>0.521</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.656</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2000,7 +2000,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -2121,35 +2121,35 @@
         <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>74</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -2171,10 +2171,10 @@
         <v>100</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.671</v>
+        <v>0.618</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>3</v>
@@ -2183,27 +2183,27 @@
         <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>11</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2269,20 +2269,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>600</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>4</v>
@@ -2291,22 +2291,22 @@
         <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -2473,16 +2473,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -2498,20 +2498,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -2527,20 +2527,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -2556,20 +2556,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -2585,20 +2585,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -2614,20 +2614,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -2643,20 +2643,20 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -2730,20 +2730,20 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>1.66</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -2766,13 +2766,13 @@
         <v>1.65</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -2962,24 +2962,24 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2995,20 +2995,20 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.1875</v>
+        <v>-0.2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3020,20 +3020,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -3049,20 +3049,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.0625</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -3078,20 +3078,20 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.125</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -3107,20 +3107,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.1875</v>
+        <v>-0.5334</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -3198,10 +3198,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.716666666666667</v>
+        <v>1.715</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
@@ -3217,10 +3217,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.725</v>
+        <v>1.743333333333333</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
@@ -3255,13 +3255,13 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2.458333333333333</v>
+        <v>2.511116666666667</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -3819,10 +3819,10 @@
         <v>100</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.671</v>
+        <v>0.618</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -3831,22 +3831,22 @@
         <v>3</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>11</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -3870,34 +3870,34 @@
         <v>100</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.596</v>
+        <v>0.613</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.612</v>
+        <v>0.627</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>15</v>
-      </c>
       <c r="N9" s="2" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>2</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3921,10 +3921,10 @@
         <v>100</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.658</v>
+        <v>0.61</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.676</v>
+        <v>0.632</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>4</v>
@@ -3933,22 +3933,22 @@
         <v>4</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>3</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -3972,10 +3972,10 @@
         <v>100</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.612</v>
+        <v>0.637</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>4</v>
@@ -3984,22 +3984,22 @@
         <v>4</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>4</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -4023,19 +4023,19 @@
         <v>100</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.616</v>
+        <v>0.584</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.632</v>
+        <v>0.599</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>1.66</v>
@@ -4044,13 +4044,13 @@
         <v>57</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>5</v>
@@ -4074,16 +4074,16 @@
         <v>100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.576</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.614</v>
+        <v>0.588</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1.66</v>
@@ -4092,16 +4092,16 @@
         <v>1.65</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>6</v>
@@ -4125,28 +4125,28 @@
         <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>74</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
@@ -4172,10 +4172,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.753</v>
+        <v>0.779</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.753</v>
+        <v>0.779</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -4184,16 +4184,16 @@
         <v>3</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -4219,28 +4219,28 @@
         <v>100</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4266,10 +4266,10 @@
         <v>100</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.704</v>
+        <v>0.676</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.704</v>
+        <v>0.676</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>3</v>
@@ -4278,16 +4278,16 @@
         <v>3</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4313,28 +4313,28 @@
         <v>100</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4360,28 +4360,28 @@
         <v>100</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.656</v>
+        <v>0.694</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.656</v>
+        <v>0.694</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
@@ -4397,20 +4397,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>4</v>
@@ -4419,22 +4419,22 @@
         <v>4</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>1</v>
@@ -4455,25 +4455,25 @@
         <v>600</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.8383</v>
+        <v>0.9367</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.86</v>
+        <v>0.9533</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.6875</v>
+        <v>2.6667</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>15</v>
@@ -4482,10 +4482,10 @@
         <v>8</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5333</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>2</v>
@@ -4499,44 +4499,44 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.7017</v>
+        <v>0.6983</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2.625</v>
+        <v>2.5333</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>3</v>
@@ -4550,20 +4550,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.6883</v>
+        <v>0.6967</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.7117</v>
+        <v>0.7167</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>3</v>
@@ -4572,22 +4572,22 @@
         <v>3</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>15</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.375</v>
+        <v>0.2667</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>4</v>
@@ -4601,44 +4601,44 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.7267</v>
+        <v>0.7133</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.7467</v>
+        <v>0.7383</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>5</v>
@@ -4652,20 +4652,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>600</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.7367</v>
+        <v>0.7667</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>4</v>
@@ -4674,10 +4674,10 @@
         <v>4</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2.25</v>
+        <v>2.5333</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>14</v>
@@ -4686,10 +4686,10 @@
         <v>5</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3125</v>
+        <v>0.4</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>6</v>

--- a/data/exports/backtesting/unified_model_performance_dashboard.xlsx
+++ b/data/exports/backtesting/unified_model_performance_dashboard.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
